--- a/artfynd/A 16347-2025 artfynd.xlsx
+++ b/artfynd/A 16347-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -813,6 +813,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133036823</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Restenäs, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>316959</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6459610</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16347-2025 artfynd.xlsx
+++ b/artfynd/A 16347-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92679637</v>
+        <v>129717967</v>
       </c>
       <c r="B2" t="n">
-        <v>4754</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100856</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Klibbtickgnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dorcatoma punctulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Mulsant &amp; Rey, 1864</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>kläckningsfälla</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Restenäs, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>316969.1165351636</v>
+        <v>317144</v>
       </c>
       <c r="R2" t="n">
-        <v>6459560.859261397</v>
+        <v>6459846</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-02-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-02-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,122 +757,108 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>klibbticka</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>Niklas Franc</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>NF19545</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Franc</t>
+          <t>Isabell Winberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niklas Franc</t>
+          <t>Isabell Winberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133036823</v>
+        <v>108217503</v>
       </c>
       <c r="B3" t="n">
-        <v>56879</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Restenäs, Boh</t>
+          <t>Lyckhem, Boh</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>316959</v>
+        <v>317066</v>
       </c>
       <c r="R3" t="n">
-        <v>6459610</v>
+        <v>6459818</v>
       </c>
       <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
         <v>1</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Uddevalla</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Bohuslän</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Resteröd</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -910,6 +875,343 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>90908596</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57959</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100046</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vitryggig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dendrocopos leucotos</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1803)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kyrkstigen, Restenäs, Resteröd, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>316993</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6459722</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1969-01-16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1969-01-16</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>"Tillfällig gäst. Denna norrländska hackspett gästade våra trakter den 16/1-69 då 1 ex iakttogs i ett mindre barrskogsområde mellan Bäck och Restenäs i Resteröd (Jan Uddén)." Ref: Uddén, J. 1977. Fåglar i södra Bohuslän. Fågellivet i Forshälla, Grinneröd, Ljung och Resteröd 1967-1976. Uddevalla. Sid 72. (Enligt raritetsrapporten (BohOF:s arkiv 76-117) var det en hona. Observationen gjordes enligt observatören (2022-11-15) vid Kyrkstigen, SV Lyckhem).</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Rune Hixén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Uddén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>92679567</v>
+      </c>
+      <c r="B5" t="n">
+        <v>4818</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100856</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Klibbtickgnagare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dorcatoma punctulata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mulsant &amp; Rey, 1864</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>kläckningsfälla</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Restenäs, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>316969</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6459561</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-02-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-02-23</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>klibbticka</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>NF19582</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Niklas Franc</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133036823</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Restenäs, Boh</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>316959</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6459610</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Uddevalla</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resteröd</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isabell Winberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 16347-2025 artfynd.xlsx
+++ b/artfynd/A 16347-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129717967</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108217503</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90908596</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92679567</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,8 +1237,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133036823</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>